--- a/data/raw/구분상가매매.xlsx
+++ b/data/raw/구분상가매매.xlsx
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3493,7 +3493,7 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4643,7 +4643,7 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4743,12 +4743,12 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -4839,7 +4839,7 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8448,7 +8448,7 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9438,7 +9438,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -9542,7 +9542,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9954,7 +9954,7 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10054,7 +10054,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -11898,7 +11898,7 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -12620,7 +12620,7 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -13006,7 +13006,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -13210,7 +13210,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -13504,7 +13504,7 @@
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -14051,7 +14051,7 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -14507,7 +14507,7 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -14599,7 +14599,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P166" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>3,232</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -17226,7 +17226,7 @@
       </c>
       <c r="O177" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P177" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -17546,7 +17546,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -17638,7 +17638,7 @@
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -17834,7 +17834,7 @@
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -19377,7 +19377,7 @@
       <c r="N199" t="inlineStr"/>
       <c r="O199" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -20259,7 +20259,7 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -20715,7 +20715,7 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -20999,7 +20999,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -21211,7 +21211,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -21403,7 +21403,7 @@
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P221" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr"/>
@@ -67381,7 +67381,7 @@
       <c r="N2128" t="inlineStr"/>
       <c r="O2128" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2128" t="inlineStr">
@@ -67477,7 +67477,7 @@
       <c r="N2131" t="inlineStr"/>
       <c r="O2131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2131" t="inlineStr">
@@ -67509,7 +67509,7 @@
       <c r="N2132" t="inlineStr"/>
       <c r="O2132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2132" t="inlineStr">
@@ -67669,7 +67669,7 @@
       <c r="N2137" t="inlineStr"/>
       <c r="O2137" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2137" t="inlineStr">
@@ -67705,7 +67705,7 @@
       <c r="N2138" t="inlineStr"/>
       <c r="O2138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2138" t="inlineStr">

--- a/data/raw/구분상가매매.xlsx
+++ b/data/raw/구분상가매매.xlsx
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4743,12 +4743,12 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9954,7 +9954,7 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -10326,7 +10326,7 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11538,7 +11538,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -11626,7 +11626,7 @@
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -11898,7 +11898,7 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -12246,7 +12246,7 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12620,7 +12620,7 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12906,7 +12906,7 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13006,7 +13006,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -13586,7 +13586,7 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -14599,7 +14599,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -15826,7 +15826,7 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -16390,7 +16390,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P169" t="inlineStr">
@@ -16566,7 +16566,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P170" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -17733,7 +17733,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="O182" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -18364,7 +18364,7 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -18649,7 +18649,7 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -19649,7 +19649,7 @@
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
@@ -19883,7 +19883,7 @@
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -20259,7 +20259,7 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -21211,7 +21211,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -21495,7 +21495,7 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -21556,7 +21556,7 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr"/>
@@ -67381,7 +67381,7 @@
       <c r="N2128" t="inlineStr"/>
       <c r="O2128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2128" t="inlineStr">
@@ -67509,7 +67509,7 @@
       <c r="N2132" t="inlineStr"/>
       <c r="O2132" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2132" t="inlineStr">
@@ -67541,7 +67541,7 @@
       <c r="N2133" t="inlineStr"/>
       <c r="O2133" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2133" t="inlineStr">
@@ -67578,7 +67578,7 @@
       </c>
       <c r="P2134" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="Q2134" t="inlineStr"/>
@@ -67669,7 +67669,7 @@
       <c r="N2137" t="inlineStr"/>
       <c r="O2137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2137" t="inlineStr">
@@ -67705,7 +67705,7 @@
       <c r="N2138" t="inlineStr"/>
       <c r="O2138" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2138" t="inlineStr">

--- a/data/raw/구분상가매매.xlsx
+++ b/data/raw/구분상가매매.xlsx
@@ -2619,7 +2619,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4743,7 +4743,7 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4939,7 +4939,7 @@
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6755,7 +6755,7 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8254,7 +8254,7 @@
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>1699.9</t>
+          <t>1699.90</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8448,7 +8448,7 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9438,7 +9438,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -9954,7 +9954,7 @@
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -10054,7 +10054,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11538,7 +11538,7 @@
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -11714,7 +11714,7 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -11806,7 +11806,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -11898,7 +11898,7 @@
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
@@ -12050,7 +12050,7 @@
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -12142,7 +12142,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12246,7 +12246,7 @@
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -13006,7 +13006,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -13875,7 +13875,7 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -14051,7 +14051,7 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
@@ -14507,7 +14507,7 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -14599,7 +14599,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P159" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -16209,7 +16209,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3,232</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P178" t="inlineStr">
@@ -18364,7 +18364,7 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -18649,7 +18649,7 @@
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -18749,7 +18749,7 @@
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -18845,7 +18845,7 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -18941,12 +18941,12 @@
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -19041,7 +19041,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -19469,7 +19469,7 @@
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -19649,7 +19649,7 @@
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -19883,7 +19883,7 @@
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -20355,7 +20355,7 @@
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -20452,7 +20452,7 @@
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -21211,7 +21211,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -21495,7 +21495,7 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -21836,7 +21836,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -22000,7 +22000,7 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -22080,7 +22080,7 @@
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -22193,22 +22193,62 @@
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>250908</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>부평동</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>199-20</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>가나베스트텔빌딩</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>드라이빙존</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>90,000</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P231" t="inlineStr">
@@ -22216,12 +22256,36 @@
           <t>4.50%</t>
         </is>
       </c>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>5000/300가능, 임차인 26.11 만기</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>010-3785-6867</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -67950,7 +68014,7 @@
       </c>
       <c r="O2133" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2133" t="inlineStr">
@@ -68038,7 +68102,7 @@
       <c r="N2135" t="inlineStr"/>
       <c r="O2135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2135" t="inlineStr">
@@ -68075,7 +68139,7 @@
       </c>
       <c r="P2136" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="Q2136" t="inlineStr"/>
@@ -68102,7 +68166,7 @@
       <c r="N2137" t="inlineStr"/>
       <c r="O2137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2137" t="inlineStr">
@@ -68134,7 +68198,7 @@
       <c r="N2138" t="inlineStr"/>
       <c r="O2138" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2138" t="inlineStr">
@@ -68166,7 +68230,7 @@
       <c r="N2139" t="inlineStr"/>
       <c r="O2139" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2139" t="inlineStr">
@@ -68198,7 +68262,7 @@
       <c r="N2140" t="inlineStr"/>
       <c r="O2140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2140" t="inlineStr">
@@ -68294,7 +68358,7 @@
       <c r="N2143" t="inlineStr"/>
       <c r="O2143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2143" t="inlineStr">

--- a/data/raw/구분상가매매.xlsx
+++ b/data/raw/구분상가매매.xlsx
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr"/>
@@ -4348,7 +4348,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4839,7 +4839,7 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5039,12 +5039,12 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6755,7 +6755,7 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7271,7 +7271,7 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8448,7 +8448,7 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10054,7 +10054,7 @@
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -10326,7 +10326,7 @@
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -12620,7 +12620,7 @@
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
@@ -12906,7 +12906,7 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -13210,7 +13210,7 @@
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -13875,7 +13875,7 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -14051,7 +14051,7 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14331,7 +14331,7 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -14507,7 +14507,7 @@
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -14599,7 +14599,7 @@
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P164" t="inlineStr">
@@ -16118,7 +16118,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P165" t="inlineStr">
@@ -16298,7 +16298,7 @@
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
@@ -16662,7 +16662,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -18156,7 +18156,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -18561,7 +18561,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -18845,7 +18845,7 @@
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -18941,12 +18941,12 @@
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="Q194" t="inlineStr">
@@ -19561,7 +19561,7 @@
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -19649,7 +19649,7 @@
       <c r="N202" t="inlineStr"/>
       <c r="O202" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P202" t="inlineStr">
@@ -20163,7 +20163,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -20452,7 +20452,7 @@
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P211" t="inlineStr">
@@ -20630,7 +20630,7 @@
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P213" t="inlineStr">
@@ -20715,7 +20715,7 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -20807,7 +20807,7 @@
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -20903,7 +20903,7 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -20999,7 +20999,7 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P217" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -21211,7 +21211,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -21315,7 +21315,7 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -21760,7 +21760,7 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -21836,7 +21836,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -21912,7 +21912,7 @@
       <c r="N227" t="inlineStr"/>
       <c r="O227" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -22080,7 +22080,7 @@
       <c r="N229" t="inlineStr"/>
       <c r="O229" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -22156,7 +22156,7 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -22193,18 +22193,58 @@
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
-      <c r="B231" t="inlineStr"/>
-      <c r="C231" t="inlineStr"/>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
-      <c r="G231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>250908</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>부평동</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>199-20</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>가나베스트텔빌딩</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>드라이빙존</t>
+        </is>
+      </c>
       <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr"/>
-      <c r="J231" t="inlineStr"/>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>90,000</t>
+        </is>
+      </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr">
         <is>
@@ -22216,12 +22256,36 @@
           <t>4.50%</t>
         </is>
       </c>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
-      <c r="U231" t="inlineStr"/>
-      <c r="V231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>3.67%</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>5000/300가능, 임차인 26.11 만기</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>남</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>생</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>임대인</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>010-3785-6867</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -68006,7 +68070,7 @@
       <c r="N2134" t="inlineStr"/>
       <c r="O2134" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2134" t="inlineStr">
@@ -68038,7 +68102,7 @@
       <c r="N2135" t="inlineStr"/>
       <c r="O2135" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2135" t="inlineStr">
@@ -68075,7 +68139,7 @@
       </c>
       <c r="P2136" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="Q2136" t="inlineStr"/>
@@ -68102,7 +68166,7 @@
       <c r="N2137" t="inlineStr"/>
       <c r="O2137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2137" t="inlineStr">
@@ -68134,7 +68198,7 @@
       <c r="N2138" t="inlineStr"/>
       <c r="O2138" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2138" t="inlineStr">
@@ -68198,7 +68262,7 @@
       <c r="N2140" t="inlineStr"/>
       <c r="O2140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2140" t="inlineStr">
@@ -68262,7 +68326,7 @@
       <c r="N2142" t="inlineStr"/>
       <c r="O2142" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2142" t="inlineStr">
@@ -68294,7 +68358,7 @@
       <c r="N2143" t="inlineStr"/>
       <c r="O2143" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2143" t="inlineStr">

--- a/data/raw/구분상가매매.xlsx
+++ b/data/raw/구분상가매매.xlsx
@@ -2531,7 +2531,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4839,7 +4839,7 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5039,7 +5039,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5323,7 +5323,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4.90%</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6755,7 +6755,7 @@
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7271,7 +7271,7 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8448,7 +8448,7 @@
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -11714,7 +11714,7 @@
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -11806,7 +11806,7 @@
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -12142,7 +12142,7 @@
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -12906,7 +12906,7 @@
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13006,7 +13006,7 @@
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -13586,7 +13586,7 @@
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P139" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -13875,7 +13875,7 @@
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -14051,7 +14051,7 @@
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr"/>
@@ -14331,7 +14331,7 @@
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -15001,7 +15001,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P154" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P156" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -16754,7 +16754,7 @@
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -16814,7 +16814,7 @@
       <c r="N173" t="inlineStr"/>
       <c r="O173" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -17122,7 +17122,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P176" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -18047,7 +18047,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -18364,7 +18364,7 @@
       <c r="N188" t="inlineStr"/>
       <c r="O188" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -19469,7 +19469,7 @@
       <c r="N200" t="inlineStr"/>
       <c r="O200" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -19561,7 +19561,7 @@
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P201" t="inlineStr">
@@ -19883,7 +19883,7 @@
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P205" t="inlineStr">
@@ -20081,12 +20081,12 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -20259,7 +20259,7 @@
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -20550,7 +20550,7 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P212" t="inlineStr">
@@ -20715,7 +20715,7 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P214" t="inlineStr">
@@ -20807,7 +20807,7 @@
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P215" t="inlineStr">
@@ -20903,7 +20903,7 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P218" t="inlineStr">
@@ -21211,7 +21211,7 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P219" t="inlineStr">
@@ -21315,7 +21315,7 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P220" t="inlineStr">
@@ -21760,7 +21760,7 @@
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -21836,7 +21836,7 @@
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -22000,7 +22000,7 @@
       <c r="N228" t="inlineStr"/>
       <c r="O228" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P228" t="inlineStr">
@@ -22156,12 +22156,12 @@
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr"/>
@@ -68198,7 +68198,7 @@
       <c r="N2138" t="inlineStr"/>
       <c r="O2138" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2138" t="inlineStr">
@@ -68230,7 +68230,7 @@
       <c r="N2139" t="inlineStr"/>
       <c r="O2139" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2139" t="inlineStr">
@@ -68326,7 +68326,7 @@
       <c r="N2142" t="inlineStr"/>
       <c r="O2142" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="P2142" t="inlineStr">
@@ -68394,7 +68394,7 @@
       <c r="N2144" t="inlineStr"/>
       <c r="O2144" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="P2144" t="inlineStr">
